--- a/database/event/5372/event_5372_evp_summary.xlsx
+++ b/database/event/5372/event_5372_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>5.5468</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1446</v>
+        <v>4.059</v>
       </c>
       <c r="E2" t="n">
         <v>11.3024</v>
@@ -514,7 +514,7 @@
         <v>4.8389</v>
       </c>
       <c r="H2" t="n">
-        <v>10.7245</v>
+        <v>10.2159</v>
       </c>
       <c r="I2" t="n">
         <v>11.3918</v>
@@ -548,7 +548,7 @@
         <v>4.4417</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2349</v>
+        <v>3.1618</v>
       </c>
       <c r="E3" t="n">
         <v>9.050599999999999</v>
@@ -560,7 +560,7 @@
         <v>2.5871</v>
       </c>
       <c r="H3" t="n">
-        <v>10.0658</v>
+        <v>9.5884</v>
       </c>
       <c r="I3" t="n">
         <v>10.6922</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.8842</v>
+        <v>8.563599999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>4.3601</v>
+        <v>4.2027</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1677</v>
+        <v>2.9678</v>
       </c>
       <c r="E4" t="n">
-        <v>8.8842</v>
+        <v>8.563599999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>6.4635</v>
+        <v>6.1429</v>
       </c>
       <c r="G4" t="n">
         <v>2.4207</v>
       </c>
       <c r="H4" t="n">
-        <v>7.839</v>
+        <v>7.329</v>
       </c>
       <c r="I4" t="n">
         <v>8.522399999999999</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.170400000000001</v>
+        <v>7.9817</v>
       </c>
       <c r="C5" t="n">
-        <v>4.0098</v>
+        <v>3.9171</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8793</v>
+        <v>2.736</v>
       </c>
       <c r="E5" t="n">
-        <v>8.170400000000001</v>
+        <v>7.9817</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1528</v>
+        <v>5.9641</v>
       </c>
       <c r="G5" t="n">
         <v>2.0176</v>
       </c>
       <c r="H5" t="n">
-        <v>7.3445</v>
+        <v>7.0486</v>
       </c>
       <c r="I5" t="n">
         <v>7.7293</v>
@@ -686,7 +686,7 @@
         <v>3.7174</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6386</v>
+        <v>2.5738</v>
       </c>
       <c r="E6" t="n">
         <v>7.5746</v>
@@ -698,7 +698,7 @@
         <v>1.1111</v>
       </c>
       <c r="H6" t="n">
-        <v>9.823600000000001</v>
+        <v>9.1845</v>
       </c>
       <c r="I6" t="n">
         <v>10.68</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.0555</v>
+        <v>6.845</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4626</v>
+        <v>3.3593</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4289</v>
+        <v>2.2831</v>
       </c>
       <c r="E7" t="n">
-        <v>7.0555</v>
+        <v>6.845</v>
       </c>
       <c r="F7" t="n">
-        <v>4.7041</v>
+        <v>4.4936</v>
       </c>
       <c r="G7" t="n">
         <v>2.3514</v>
       </c>
       <c r="H7" t="n">
-        <v>5.073</v>
+        <v>4.7429</v>
       </c>
       <c r="I7" t="n">
         <v>5.5153</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.9435</v>
+        <v>6.8421</v>
       </c>
       <c r="C8" t="n">
-        <v>3.4076</v>
+        <v>3.3579</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3837</v>
+        <v>2.282</v>
       </c>
       <c r="E8" t="n">
-        <v>6.9435</v>
+        <v>6.8421</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3122</v>
+        <v>2.2108</v>
       </c>
       <c r="G8" t="n">
         <v>4.6313</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3122</v>
+        <v>2.2108</v>
       </c>
       <c r="I8" t="n">
         <v>2.4447</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.8418</v>
+        <v>6.6934</v>
       </c>
       <c r="C9" t="n">
-        <v>3.3577</v>
+        <v>3.2849</v>
       </c>
       <c r="D9" t="n">
-        <v>2.3426</v>
+        <v>2.2227</v>
       </c>
       <c r="E9" t="n">
-        <v>6.8418</v>
+        <v>6.6934</v>
       </c>
       <c r="F9" t="n">
-        <v>4.5987</v>
+        <v>4.4503</v>
       </c>
       <c r="G9" t="n">
         <v>2.2431</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9077</v>
+        <v>4.675</v>
       </c>
       <c r="I9" t="n">
         <v>5.2131</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.7602</v>
+        <v>6.6084</v>
       </c>
       <c r="C10" t="n">
-        <v>3.3177</v>
+        <v>3.2432</v>
       </c>
       <c r="D10" t="n">
-        <v>2.3096</v>
+        <v>2.1889</v>
       </c>
       <c r="E10" t="n">
-        <v>6.7602</v>
+        <v>6.6084</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4609</v>
+        <v>3.3091</v>
       </c>
       <c r="G10" t="n">
         <v>3.2993</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4609</v>
+        <v>3.3091</v>
       </c>
       <c r="I10" t="n">
         <v>3.6593</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.4043</v>
+        <v>6.2927</v>
       </c>
       <c r="C11" t="n">
-        <v>3.143</v>
+        <v>3.0882</v>
       </c>
       <c r="D11" t="n">
-        <v>2.1658</v>
+        <v>2.0631</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4043</v>
+        <v>6.2927</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2414</v>
+        <v>4.1298</v>
       </c>
       <c r="G11" t="n">
         <v>2.1629</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3475</v>
+        <v>4.1724</v>
       </c>
       <c r="I11" t="n">
         <v>4.5754</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.2676</v>
+        <v>6.0536</v>
       </c>
       <c r="C12" t="n">
-        <v>3.0759</v>
+        <v>2.9709</v>
       </c>
       <c r="D12" t="n">
-        <v>2.1106</v>
+        <v>1.9678</v>
       </c>
       <c r="E12" t="n">
-        <v>6.2676</v>
+        <v>6.0536</v>
       </c>
       <c r="F12" t="n">
-        <v>6.4635</v>
+        <v>6.2495</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1959</v>
       </c>
       <c r="H12" t="n">
-        <v>8.017799999999999</v>
+        <v>7.4961</v>
       </c>
       <c r="I12" t="n">
         <v>8.716699999999999</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.1543</v>
+        <v>6.037</v>
       </c>
       <c r="C13" t="n">
-        <v>3.0203</v>
+        <v>2.9628</v>
       </c>
       <c r="D13" t="n">
-        <v>2.0648</v>
+        <v>1.9612</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1543</v>
+        <v>6.037</v>
       </c>
       <c r="F13" t="n">
-        <v>4.3803</v>
+        <v>4.263</v>
       </c>
       <c r="G13" t="n">
         <v>1.774</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5652</v>
+        <v>4.3813</v>
       </c>
       <c r="I13" t="n">
         <v>4.8045</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.0125</v>
+        <v>5.8787</v>
       </c>
       <c r="C14" t="n">
-        <v>2.9507</v>
+        <v>2.8851</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0076</v>
+        <v>1.8982</v>
       </c>
       <c r="E14" t="n">
-        <v>6.0125</v>
+        <v>5.8787</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0125</v>
+        <v>5.8787</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>7.1245</v>
+        <v>6.9147</v>
       </c>
       <c r="I14" t="n">
         <v>7.3942</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.9228</v>
+        <v>5.7702</v>
       </c>
       <c r="C15" t="n">
-        <v>2.9067</v>
+        <v>2.8318</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9713</v>
+        <v>1.8549</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9228</v>
+        <v>5.7702</v>
       </c>
       <c r="F15" t="n">
-        <v>5.6297</v>
+        <v>5.4771</v>
       </c>
       <c r="G15" t="n">
         <v>0.2931</v>
       </c>
       <c r="H15" t="n">
-        <v>6.5243</v>
+        <v>6.285</v>
       </c>
       <c r="I15" t="n">
         <v>6.8344</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.8458</v>
+        <v>5.6886</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8689</v>
+        <v>2.7918</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9402</v>
+        <v>1.8224</v>
       </c>
       <c r="E16" t="n">
-        <v>5.8458</v>
+        <v>5.6886</v>
       </c>
       <c r="F16" t="n">
-        <v>5.054</v>
+        <v>4.8968</v>
       </c>
       <c r="G16" t="n">
         <v>0.7917999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>5.6216</v>
+        <v>5.3751</v>
       </c>
       <c r="I16" t="n">
         <v>5.9438</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.6164</v>
+        <v>5.5399</v>
       </c>
       <c r="C17" t="n">
-        <v>2.7563</v>
+        <v>2.7188</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8475</v>
+        <v>1.7632</v>
       </c>
       <c r="E17" t="n">
-        <v>5.6164</v>
+        <v>5.5399</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8997</v>
+        <v>1.8232</v>
       </c>
       <c r="G17" t="n">
         <v>3.7167</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8997</v>
+        <v>1.8232</v>
       </c>
       <c r="I17" t="n">
         <v>1.9993</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5.2673</v>
+        <v>5.109</v>
       </c>
       <c r="C18" t="n">
-        <v>2.585</v>
+        <v>2.5073</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7065</v>
+        <v>1.5915</v>
       </c>
       <c r="E18" t="n">
-        <v>5.2673</v>
+        <v>5.109</v>
       </c>
       <c r="F18" t="n">
-        <v>5.3992</v>
+        <v>5.2409</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1319</v>
       </c>
       <c r="H18" t="n">
-        <v>6.1629</v>
+        <v>5.9146</v>
       </c>
       <c r="I18" t="n">
         <v>6.4859</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.058</v>
+        <v>4.8655</v>
       </c>
       <c r="C19" t="n">
-        <v>2.4823</v>
+        <v>2.3878</v>
       </c>
       <c r="D19" t="n">
-        <v>1.622</v>
+        <v>1.4945</v>
       </c>
       <c r="E19" t="n">
-        <v>5.058</v>
+        <v>4.8655</v>
       </c>
       <c r="F19" t="n">
-        <v>6.2486</v>
+        <v>6.0561</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1906</v>
       </c>
       <c r="H19" t="n">
-        <v>7.4947</v>
+        <v>7.1928</v>
       </c>
       <c r="I19" t="n">
         <v>7.8875</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.9436</v>
+        <v>4.8413</v>
       </c>
       <c r="C20" t="n">
-        <v>2.4262</v>
+        <v>2.3759</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5757</v>
+        <v>1.4849</v>
       </c>
       <c r="E20" t="n">
-        <v>4.9436</v>
+        <v>4.8413</v>
       </c>
       <c r="F20" t="n">
-        <v>4.9436</v>
+        <v>4.8413</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4486</v>
+        <v>5.288</v>
       </c>
       <c r="I20" t="n">
         <v>5.6548</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.8187</v>
+        <v>4.718</v>
       </c>
       <c r="C21" t="n">
-        <v>2.3649</v>
+        <v>2.3154</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5253</v>
+        <v>1.4357</v>
       </c>
       <c r="E21" t="n">
-        <v>4.8187</v>
+        <v>4.718</v>
       </c>
       <c r="F21" t="n">
-        <v>2.209</v>
+        <v>4.718</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6097</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.209</v>
+        <v>5.0948</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3465</v>
+        <v>5.4482</v>
       </c>
       <c r="J21" t="n">
-        <v>2.6097</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>637</v>
+        <v>455</v>
       </c>
       <c r="L21" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.9562</v>
+        <v>5.4482</v>
       </c>
       <c r="N21" t="n">
-        <v>797</v>
+        <v>455</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.8167</v>
+        <v>4.7139</v>
       </c>
       <c r="C22" t="n">
-        <v>2.3639</v>
+        <v>2.3134</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5245</v>
+        <v>1.4341</v>
       </c>
       <c r="E22" t="n">
-        <v>4.8167</v>
+        <v>4.7139</v>
       </c>
       <c r="F22" t="n">
-        <v>4.8167</v>
+        <v>2.1042</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2.6097</v>
       </c>
       <c r="H22" t="n">
-        <v>5.2495</v>
+        <v>2.1042</v>
       </c>
       <c r="I22" t="n">
-        <v>5.4482</v>
+        <v>2.3465</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2.6097</v>
       </c>
       <c r="K22" t="n">
-        <v>455</v>
+        <v>637</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M22" t="n">
-        <v>5.4482</v>
+        <v>4.9562</v>
       </c>
       <c r="N22" t="n">
-        <v>455</v>
+        <v>797</v>
       </c>
     </row>
     <row r="23">
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.3655</v>
+        <v>4.2801</v>
       </c>
       <c r="C23" t="n">
-        <v>2.1424</v>
+        <v>2.1005</v>
       </c>
       <c r="D23" t="n">
-        <v>1.3422</v>
+        <v>1.2613</v>
       </c>
       <c r="E23" t="n">
-        <v>4.3655</v>
+        <v>4.2801</v>
       </c>
       <c r="F23" t="n">
-        <v>4.3655</v>
+        <v>4.2801</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>4.542</v>
+        <v>4.4082</v>
       </c>
       <c r="I23" t="n">
         <v>4.7139</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.0029</v>
+        <v>3.9069</v>
       </c>
       <c r="C24" t="n">
-        <v>1.9645</v>
+        <v>1.9174</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1957</v>
+        <v>1.1126</v>
       </c>
       <c r="E24" t="n">
-        <v>4.0029</v>
+        <v>3.9069</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0243</v>
+        <v>1.9283</v>
       </c>
       <c r="G24" t="n">
         <v>1.9786</v>
       </c>
       <c r="H24" t="n">
-        <v>2.0243</v>
+        <v>1.9283</v>
       </c>
       <c r="I24" t="n">
         <v>2.1502</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.9836</v>
+        <v>3.867</v>
       </c>
       <c r="C25" t="n">
-        <v>1.955</v>
+        <v>1.8978</v>
       </c>
       <c r="D25" t="n">
-        <v>1.1879</v>
+        <v>1.0967</v>
       </c>
       <c r="E25" t="n">
-        <v>3.9836</v>
+        <v>3.867</v>
       </c>
       <c r="F25" t="n">
-        <v>4.1473</v>
+        <v>4.0307</v>
       </c>
       <c r="G25" t="n">
         <v>-0.1637</v>
       </c>
       <c r="H25" t="n">
-        <v>4.1999</v>
+        <v>4.0307</v>
       </c>
       <c r="I25" t="n">
         <v>4.42</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.9678</v>
+        <v>3.8365</v>
       </c>
       <c r="C26" t="n">
-        <v>1.9473</v>
+        <v>1.8828</v>
       </c>
       <c r="D26" t="n">
-        <v>1.1815</v>
+        <v>1.0846</v>
       </c>
       <c r="E26" t="n">
-        <v>3.9678</v>
+        <v>3.8365</v>
       </c>
       <c r="F26" t="n">
-        <v>3.9678</v>
+        <v>3.8365</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3.9678</v>
+        <v>3.8365</v>
       </c>
       <c r="I26" t="n">
         <v>4.1371</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.9263</v>
+        <v>3.8249</v>
       </c>
       <c r="C27" t="n">
-        <v>1.9269</v>
+        <v>1.8771</v>
       </c>
       <c r="D27" t="n">
-        <v>1.1648</v>
+        <v>1.0799</v>
       </c>
       <c r="E27" t="n">
-        <v>3.9263</v>
+        <v>3.8249</v>
       </c>
       <c r="F27" t="n">
-        <v>3.9263</v>
+        <v>3.8249</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3.9263</v>
+        <v>3.8249</v>
       </c>
       <c r="I27" t="n">
         <v>4.056</v>
@@ -1688,93 +1688,93 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.8572</v>
+        <v>3.6712</v>
       </c>
       <c r="C28" t="n">
-        <v>1.893</v>
+        <v>1.8017</v>
       </c>
       <c r="D28" t="n">
-        <v>1.1369</v>
+        <v>1.0187</v>
       </c>
       <c r="E28" t="n">
-        <v>3.8572</v>
+        <v>3.6712</v>
       </c>
       <c r="F28" t="n">
-        <v>4.5081</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.6509</v>
+        <v>3.1444</v>
       </c>
       <c r="H28" t="n">
-        <v>4.7656</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>5.1811</v>
+        <v>0.5825</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6509</v>
+        <v>3.1444</v>
       </c>
       <c r="K28" t="n">
-        <v>639</v>
+        <v>702</v>
       </c>
       <c r="L28" t="n">
-        <v>192</v>
+        <v>88</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5302</v>
+        <v>3.7269</v>
       </c>
       <c r="N28" t="n">
-        <v>831</v>
+        <v>790</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>oBo</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.7583</v>
+        <v>3.6594</v>
       </c>
       <c r="C29" t="n">
-        <v>1.8444</v>
+        <v>1.7959</v>
       </c>
       <c r="D29" t="n">
-        <v>1.0969</v>
+        <v>1.014</v>
       </c>
       <c r="E29" t="n">
-        <v>3.7583</v>
+        <v>3.6594</v>
       </c>
       <c r="F29" t="n">
-        <v>3.7583</v>
+        <v>4.3103</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.6509</v>
       </c>
       <c r="H29" t="n">
-        <v>3.7583</v>
+        <v>4.4555</v>
       </c>
       <c r="I29" t="n">
-        <v>3.9553</v>
+        <v>5.1811</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.6509</v>
       </c>
       <c r="K29" t="n">
-        <v>490</v>
+        <v>639</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="M29" t="n">
-        <v>3.9553</v>
+        <v>4.5302</v>
       </c>
       <c r="N29" t="n">
-        <v>490</v>
+        <v>831</v>
       </c>
     </row>
     <row r="30">
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3.7419</v>
+        <v>3.6452</v>
       </c>
       <c r="C30" t="n">
-        <v>1.8364</v>
+        <v>1.7889</v>
       </c>
       <c r="D30" t="n">
-        <v>1.0903</v>
+        <v>1.0083</v>
       </c>
       <c r="E30" t="n">
-        <v>3.7419</v>
+        <v>3.6452</v>
       </c>
       <c r="F30" t="n">
-        <v>3.7419</v>
+        <v>3.6452</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3.7419</v>
+        <v>3.6452</v>
       </c>
       <c r="I30" t="n">
         <v>3.8655</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.7231</v>
+        <v>3.6269</v>
       </c>
       <c r="C31" t="n">
-        <v>1.8272</v>
+        <v>1.78</v>
       </c>
       <c r="D31" t="n">
-        <v>1.0827</v>
+        <v>1.001</v>
       </c>
       <c r="E31" t="n">
-        <v>3.7231</v>
+        <v>3.6269</v>
       </c>
       <c r="F31" t="n">
-        <v>3.7231</v>
+        <v>3.6269</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3.7231</v>
+        <v>3.6269</v>
       </c>
       <c r="I31" t="n">
         <v>3.8461</v>
@@ -1872,47 +1872,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>oBo</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.6953</v>
+        <v>3.607</v>
       </c>
       <c r="C32" t="n">
-        <v>1.8135</v>
+        <v>1.7702</v>
       </c>
       <c r="D32" t="n">
-        <v>1.0715</v>
+        <v>0.9931</v>
       </c>
       <c r="E32" t="n">
-        <v>3.6953</v>
+        <v>3.607</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5508999999999999</v>
+        <v>3.607</v>
       </c>
       <c r="G32" t="n">
-        <v>3.1444</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5508999999999999</v>
+        <v>3.607</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5825</v>
+        <v>3.9553</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1444</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>702</v>
+        <v>490</v>
       </c>
       <c r="L32" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7269</v>
+        <v>3.9553</v>
       </c>
       <c r="N32" t="n">
-        <v>790</v>
+        <v>490</v>
       </c>
     </row>
     <row r="33">
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.6713</v>
+        <v>3.5156</v>
       </c>
       <c r="C33" t="n">
-        <v>1.8017</v>
+        <v>1.7253</v>
       </c>
       <c r="D33" t="n">
-        <v>1.0618</v>
+        <v>0.9567</v>
       </c>
       <c r="E33" t="n">
-        <v>3.6713</v>
+        <v>3.5156</v>
       </c>
       <c r="F33" t="n">
-        <v>3.2833</v>
+        <v>3.1276</v>
       </c>
       <c r="G33" t="n">
         <v>0.388</v>
       </c>
       <c r="H33" t="n">
-        <v>3.2833</v>
+        <v>3.1276</v>
       </c>
       <c r="I33" t="n">
         <v>3.4876</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.5756</v>
+        <v>3.4162</v>
       </c>
       <c r="C34" t="n">
-        <v>1.7548</v>
+        <v>1.6766</v>
       </c>
       <c r="D34" t="n">
-        <v>1.0231</v>
+        <v>0.9171</v>
       </c>
       <c r="E34" t="n">
-        <v>3.5756</v>
+        <v>3.4162</v>
       </c>
       <c r="F34" t="n">
-        <v>4.1516</v>
+        <v>3.9922</v>
       </c>
       <c r="G34" t="n">
         <v>-0.576</v>
       </c>
       <c r="H34" t="n">
-        <v>4.2066</v>
+        <v>3.9922</v>
       </c>
       <c r="I34" t="n">
         <v>4.4892</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.4403</v>
+        <v>3.3389</v>
       </c>
       <c r="C35" t="n">
-        <v>1.6884</v>
+        <v>1.6386</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9684</v>
+        <v>0.8863</v>
       </c>
       <c r="E35" t="n">
-        <v>3.4403</v>
+        <v>3.3389</v>
       </c>
       <c r="F35" t="n">
-        <v>3.4403</v>
+        <v>3.3389</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>3.4403</v>
+        <v>3.3389</v>
       </c>
       <c r="I35" t="n">
         <v>3.5705</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.1126</v>
+        <v>3.0665</v>
       </c>
       <c r="C36" t="n">
-        <v>1.5276</v>
+        <v>1.5049</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8361</v>
+        <v>0.7778</v>
       </c>
       <c r="E36" t="n">
-        <v>3.1126</v>
+        <v>3.0665</v>
       </c>
       <c r="F36" t="n">
-        <v>3.1126</v>
+        <v>3.0665</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3.1126</v>
+        <v>3.0665</v>
       </c>
       <c r="I36" t="n">
         <v>3.171</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.6027</v>
+        <v>2.5355</v>
       </c>
       <c r="C37" t="n">
-        <v>1.2773</v>
+        <v>1.2443</v>
       </c>
       <c r="D37" t="n">
-        <v>0.6301</v>
+        <v>0.5662</v>
       </c>
       <c r="E37" t="n">
-        <v>2.6027</v>
+        <v>2.5355</v>
       </c>
       <c r="F37" t="n">
-        <v>2.6027</v>
+        <v>2.5355</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2.6027</v>
+        <v>2.5355</v>
       </c>
       <c r="I37" t="n">
         <v>2.6887</v>
@@ -2148,93 +2148,93 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.5439</v>
+        <v>2.4149</v>
       </c>
       <c r="C38" t="n">
-        <v>1.2485</v>
+        <v>1.1852</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6063</v>
+        <v>0.5182</v>
       </c>
       <c r="E38" t="n">
-        <v>2.5439</v>
+        <v>2.4149</v>
       </c>
       <c r="F38" t="n">
-        <v>2.6431</v>
+        <v>2.4149</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0992</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2.6431</v>
+        <v>2.4149</v>
       </c>
       <c r="I38" t="n">
-        <v>2.8206</v>
+        <v>2.6041</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.0992</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>518</v>
+        <v>476</v>
       </c>
       <c r="L38" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2.7214</v>
+        <v>2.6041</v>
       </c>
       <c r="N38" t="n">
-        <v>747</v>
+        <v>476</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.4975</v>
+        <v>2.4091</v>
       </c>
       <c r="C39" t="n">
-        <v>1.2257</v>
+        <v>1.1823</v>
       </c>
       <c r="D39" t="n">
-        <v>0.5876</v>
+        <v>0.5159</v>
       </c>
       <c r="E39" t="n">
-        <v>2.4975</v>
+        <v>2.4091</v>
       </c>
       <c r="F39" t="n">
-        <v>2.4975</v>
+        <v>2.5083</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.0992</v>
       </c>
       <c r="H39" t="n">
-        <v>2.4975</v>
+        <v>2.5083</v>
       </c>
       <c r="I39" t="n">
-        <v>2.6041</v>
+        <v>2.8206</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.0992</v>
       </c>
       <c r="K39" t="n">
-        <v>476</v>
+        <v>518</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="M39" t="n">
-        <v>2.6041</v>
+        <v>2.7214</v>
       </c>
       <c r="N39" t="n">
-        <v>476</v>
+        <v>747</v>
       </c>
     </row>
     <row r="40">
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.2877</v>
+        <v>2.227</v>
       </c>
       <c r="C40" t="n">
-        <v>1.1227</v>
+        <v>1.0929</v>
       </c>
       <c r="D40" t="n">
-        <v>0.5028</v>
+        <v>0.4433</v>
       </c>
       <c r="E40" t="n">
-        <v>2.2877</v>
+        <v>2.227</v>
       </c>
       <c r="F40" t="n">
-        <v>1.5046</v>
+        <v>1.4439</v>
       </c>
       <c r="G40" t="n">
         <v>0.7831</v>
       </c>
       <c r="H40" t="n">
-        <v>1.5046</v>
+        <v>1.4439</v>
       </c>
       <c r="I40" t="n">
         <v>1.5834</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.2683</v>
+        <v>2.2097</v>
       </c>
       <c r="C41" t="n">
-        <v>1.1132</v>
+        <v>1.0844</v>
       </c>
       <c r="D41" t="n">
-        <v>0.495</v>
+        <v>0.4364</v>
       </c>
       <c r="E41" t="n">
-        <v>2.2683</v>
+        <v>2.2097</v>
       </c>
       <c r="F41" t="n">
-        <v>2.2683</v>
+        <v>2.2097</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2.2683</v>
+        <v>2.2097</v>
       </c>
       <c r="I41" t="n">
         <v>2.3432</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.0489</v>
+        <v>1.9811</v>
       </c>
       <c r="C42" t="n">
-        <v>1.0055</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>0.4063</v>
+        <v>0.3454</v>
       </c>
       <c r="E42" t="n">
-        <v>2.0489</v>
+        <v>1.9811</v>
       </c>
       <c r="F42" t="n">
-        <v>2.0489</v>
+        <v>1.9811</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2.0489</v>
+        <v>1.9811</v>
       </c>
       <c r="I42" t="n">
         <v>2.1363</v>
@@ -2382,25 +2382,25 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.02</v>
+        <v>1.8939</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9913</v>
+        <v>0.9295</v>
       </c>
       <c r="D43" t="n">
-        <v>0.3947</v>
+        <v>0.3106</v>
       </c>
       <c r="E43" t="n">
-        <v>2.02</v>
+        <v>1.8939</v>
       </c>
       <c r="F43" t="n">
-        <v>2.8734</v>
+        <v>2.7473</v>
       </c>
       <c r="G43" t="n">
         <v>-0.8534</v>
       </c>
       <c r="H43" t="n">
-        <v>2.8734</v>
+        <v>2.7473</v>
       </c>
       <c r="I43" t="n">
         <v>3.038</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.78</v>
+        <v>1.734</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8736</v>
+        <v>0.851</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2977</v>
+        <v>0.2469</v>
       </c>
       <c r="E44" t="n">
-        <v>1.78</v>
+        <v>1.734</v>
       </c>
       <c r="F44" t="n">
-        <v>1.78</v>
+        <v>1.734</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.78</v>
+        <v>1.734</v>
       </c>
       <c r="I44" t="n">
         <v>1.8388</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.7091</v>
+        <v>1.6774</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8388</v>
+        <v>0.8232</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2691</v>
+        <v>0.2244</v>
       </c>
       <c r="E45" t="n">
-        <v>1.7091</v>
+        <v>1.6774</v>
       </c>
       <c r="F45" t="n">
-        <v>1.7091</v>
+        <v>1.6774</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.7091</v>
+        <v>1.6774</v>
       </c>
       <c r="I45" t="n">
         <v>1.7492</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.6119</v>
+        <v>1.5821</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7911</v>
+        <v>0.7764</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2298</v>
+        <v>0.1864</v>
       </c>
       <c r="E46" t="n">
-        <v>1.6119</v>
+        <v>1.5821</v>
       </c>
       <c r="F46" t="n">
-        <v>1.6119</v>
+        <v>1.5821</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.6119</v>
+        <v>1.5821</v>
       </c>
       <c r="I46" t="n">
         <v>1.6498</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.3135</v>
+        <v>1.2796</v>
       </c>
       <c r="C47" t="n">
-        <v>0.6446</v>
+        <v>0.628</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1093</v>
+        <v>0.0659</v>
       </c>
       <c r="E47" t="n">
-        <v>1.3135</v>
+        <v>1.2796</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3135</v>
+        <v>1.2796</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.3135</v>
+        <v>1.2796</v>
       </c>
       <c r="I47" t="n">
         <v>1.3569</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.1375</v>
+        <v>1.069</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5582</v>
+        <v>0.5246</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0382</v>
+        <v>-0.018</v>
       </c>
       <c r="E48" t="n">
-        <v>1.1375</v>
+        <v>1.069</v>
       </c>
       <c r="F48" t="n">
-        <v>1.8673</v>
+        <v>1.7988</v>
       </c>
       <c r="G48" t="n">
         <v>-0.7298</v>
       </c>
       <c r="H48" t="n">
-        <v>1.8673</v>
+        <v>1.7988</v>
       </c>
       <c r="I48" t="n">
         <v>1.956</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8865</v>
+        <v>0.8771</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4351</v>
+        <v>0.4305</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.06320000000000001</v>
+        <v>-0.0945</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8865</v>
+        <v>0.8771</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2137</v>
+        <v>0.2043</v>
       </c>
       <c r="G49" t="n">
         <v>0.6728</v>
       </c>
       <c r="H49" t="n">
-        <v>0.2137</v>
+        <v>0.2043</v>
       </c>
       <c r="I49" t="n">
         <v>0.2259</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8321</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4208</v>
+        <v>0.4084</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.075</v>
+        <v>-0.1124</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8321</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8321</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8321</v>
       </c>
       <c r="I50" t="n">
         <v>0.8898</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6947</v>
+        <v>0.6742</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3409</v>
+        <v>0.3309</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.1407</v>
+        <v>-0.1753</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6947</v>
+        <v>0.6742</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6947</v>
+        <v>0.6742</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6947</v>
+        <v>0.6742</v>
       </c>
       <c r="I51" t="n">
         <v>0.721</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.6146</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3084</v>
+        <v>0.3016</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.1675</v>
+        <v>-0.1991</v>
       </c>
       <c r="E52" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.6146</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.6146</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.6146</v>
       </c>
       <c r="I52" t="n">
         <v>0.6463</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5437</v>
+        <v>0.5317</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2668</v>
+        <v>0.2609</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.2017</v>
+        <v>-0.2321</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5437</v>
+        <v>0.5317</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5437</v>
+        <v>0.5317</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5437</v>
+        <v>0.5317</v>
       </c>
       <c r="I53" t="n">
         <v>0.5591</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4612</v>
+        <v>0.4543</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2263</v>
+        <v>0.223</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.235</v>
+        <v>-0.2629</v>
       </c>
       <c r="E54" t="n">
-        <v>0.4612</v>
+        <v>0.4543</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4612</v>
+        <v>0.4543</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.4612</v>
+        <v>0.4543</v>
       </c>
       <c r="I54" t="n">
         <v>0.4698</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4188</v>
+        <v>0.4065</v>
       </c>
       <c r="C55" t="n">
-        <v>0.2055</v>
+        <v>0.1995</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.2522</v>
+        <v>-0.282</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4188</v>
+        <v>0.4065</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4188</v>
+        <v>0.4065</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.4188</v>
+        <v>0.4065</v>
       </c>
       <c r="I55" t="n">
         <v>0.4347</v>
@@ -2976,93 +2976,93 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>iDISBALANCE</t>
+          <t>mhL</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.3674</v>
+        <v>0.3554</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1803</v>
+        <v>0.1744</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.2729</v>
+        <v>-0.3023</v>
       </c>
       <c r="E56" t="n">
-        <v>0.3674</v>
+        <v>0.3554</v>
       </c>
       <c r="F56" t="n">
-        <v>1.067</v>
+        <v>0.3554</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.6996</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1.067</v>
+        <v>0.3554</v>
       </c>
       <c r="I56" t="n">
-        <v>1.1177</v>
+        <v>0.3737</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.6996</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>572</v>
+        <v>473</v>
       </c>
       <c r="L56" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.4180999999999999</v>
+        <v>0.3737</v>
       </c>
       <c r="N56" t="n">
-        <v>622</v>
+        <v>473</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>mhL</t>
+          <t>iDISBALANCE</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3634</v>
+        <v>0.3282</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1783</v>
+        <v>0.1611</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.2746</v>
+        <v>-0.3132</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3634</v>
+        <v>0.3282</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3634</v>
+        <v>1.0278</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-0.6996</v>
       </c>
       <c r="H57" t="n">
-        <v>0.3634</v>
+        <v>1.0278</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3737</v>
+        <v>1.1177</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>-0.6996</v>
       </c>
       <c r="K57" t="n">
-        <v>473</v>
+        <v>572</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M57" t="n">
-        <v>0.3737</v>
+        <v>0.4180999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>473</v>
+        <v>622</v>
       </c>
     </row>
     <row r="58">
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.2169</v>
+        <v>0.2121</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1064</v>
+        <v>0.1041</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.3337</v>
+        <v>-0.3594</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2169</v>
+        <v>0.2121</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2169</v>
+        <v>0.2121</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2169</v>
+        <v>0.2121</v>
       </c>
       <c r="I58" t="n">
         <v>0.223</v>
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0444</v>
+        <v>0.0393</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0218</v>
+        <v>0.0193</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.4034</v>
+        <v>-0.4283</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0444</v>
+        <v>0.0393</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1401</v>
+        <v>0.135</v>
       </c>
       <c r="G59" t="n">
         <v>-0.09569999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1401</v>
+        <v>0.135</v>
       </c>
       <c r="I59" t="n">
         <v>0.1468</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0381</v>
+        <v>0.0375</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0187</v>
+        <v>0.0184</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.406</v>
+        <v>-0.429</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0381</v>
+        <v>0.0375</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0381</v>
+        <v>0.0375</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0381</v>
+        <v>0.0375</v>
       </c>
       <c r="I60" t="n">
         <v>0.0388</v>
@@ -3216,7 +3216,7 @@
         <v>0.0074</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.4153</v>
+        <v>-0.4379</v>
       </c>
       <c r="E61" t="n">
         <v>0.0151</v>
@@ -3256,25 +3256,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.2255</v>
+        <v>-0.2221</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1107</v>
+        <v>-0.109</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5125</v>
+        <v>-0.5324</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.2255</v>
+        <v>-0.2221</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2255</v>
+        <v>-0.2221</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.2255</v>
+        <v>-0.2221</v>
       </c>
       <c r="I62" t="n">
         <v>-0.2297</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.2364</v>
+        <v>-0.2294</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.116</v>
+        <v>-0.1126</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.5169</v>
+        <v>-0.5353</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.2364</v>
+        <v>-0.2294</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.2364</v>
+        <v>-0.2294</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.2364</v>
+        <v>-0.2294</v>
       </c>
       <c r="I63" t="n">
         <v>-0.2453</v>
@@ -3354,7 +3354,7 @@
         <v>-0.154</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.5481</v>
+        <v>-0.5689</v>
       </c>
       <c r="E64" t="n">
         <v>-0.3138</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.3495</v>
+        <v>-0.343</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1715</v>
+        <v>-0.1683</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.5626</v>
+        <v>-0.5806</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.3495</v>
+        <v>-0.343</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.3495</v>
+        <v>-0.343</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.3495</v>
+        <v>-0.343</v>
       </c>
       <c r="I65" t="n">
         <v>-0.3577</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.4429</v>
+        <v>-0.4363</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2174</v>
+        <v>-0.2141</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.6177</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4429</v>
+        <v>-0.4363</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4429</v>
+        <v>-0.4363</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.4429</v>
+        <v>-0.4363</v>
       </c>
       <c r="I66" t="n">
         <v>-0.4512</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.7232</v>
+        <v>-0.7271</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.3549</v>
+        <v>-0.3568</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7135</v>
+        <v>-0.7336</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.7232</v>
+        <v>-0.7271</v>
       </c>
       <c r="F67" t="n">
-        <v>0.0902</v>
+        <v>0.0863</v>
       </c>
       <c r="G67" t="n">
         <v>-0.8134</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0902</v>
+        <v>0.0863</v>
       </c>
       <c r="I67" t="n">
         <v>0.0954</v>
@@ -3538,7 +3538,7 @@
         <v>-0.3951</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.7466</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="E68" t="n">
         <v>-0.805</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.9071</v>
+        <v>-0.8771</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4452</v>
+        <v>-0.4305</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.7933</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.9071</v>
+        <v>-0.8771</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.9071</v>
+        <v>-0.8771</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.9071</v>
+        <v>-0.8771</v>
       </c>
       <c r="I69" t="n">
         <v>-0.9458</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.1412</v>
+        <v>-1.1076</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5601</v>
+        <v>-0.5436</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8824</v>
+        <v>-0.8852</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.1412</v>
+        <v>-1.1076</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.1412</v>
+        <v>-1.1076</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.1412</v>
+        <v>-1.1076</v>
       </c>
       <c r="I70" t="n">
         <v>-1.1844</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.2036</v>
+        <v>-1.1638</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5907</v>
+        <v>-0.5712</v>
       </c>
       <c r="D71" t="n">
         <v>-0.9076</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.2036</v>
+        <v>-1.1638</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.2036</v>
+        <v>-1.1638</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.2036</v>
+        <v>-1.1638</v>
       </c>
       <c r="I71" t="n">
         <v>-1.255</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.3007</v>
+        <v>-1.2671</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6383</v>
+        <v>-0.6218</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9468</v>
+        <v>-0.9487</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.3007</v>
+        <v>-1.2671</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.3007</v>
+        <v>-1.2671</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.3007</v>
+        <v>-1.2671</v>
       </c>
       <c r="I72" t="n">
         <v>-1.3437</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.5608</v>
+        <v>-1.5029</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.766</v>
+        <v>-0.7376</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0519</v>
+        <v>-1.0427</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.5608</v>
+        <v>-1.5029</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.5792</v>
+        <v>-1.5213</v>
       </c>
       <c r="G73" t="n">
         <v>0.0184</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.5792</v>
+        <v>-1.5213</v>
       </c>
       <c r="I73" t="n">
         <v>-1.6543</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.9331</v>
+        <v>-1.8385</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.9487</v>
+        <v>-0.9023</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2023</v>
+        <v>-1.1764</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.9331</v>
+        <v>-1.8385</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.9954</v>
+        <v>-1.9008</v>
       </c>
       <c r="G74" t="n">
         <v>0.0623</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.9954</v>
+        <v>-1.9008</v>
       </c>
       <c r="I74" t="n">
         <v>-2.1196</v>
@@ -3850,139 +3850,139 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.9846</v>
+        <v>-1.9416</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.974</v>
+        <v>-0.9529</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2231</v>
+        <v>-1.2174</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.9846</v>
+        <v>-1.9416</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.9846</v>
+        <v>-1.3544</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.9846</v>
+        <v>-1.3544</v>
       </c>
       <c r="I75" t="n">
-        <v>-2.0312</v>
+        <v>-1.4977</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>417</v>
+        <v>555</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="M75" t="n">
-        <v>-2.0312</v>
+        <v>-2.0849</v>
       </c>
       <c r="N75" t="n">
-        <v>417</v>
+        <v>628</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>THREAT</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-2</v>
+        <v>-1.9478</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.9815</v>
+        <v>-0.9559</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2293</v>
+        <v>-1.2199</v>
       </c>
       <c r="E76" t="n">
-        <v>-2</v>
+        <v>-1.9478</v>
       </c>
       <c r="F76" t="n">
-        <v>-2</v>
+        <v>-1.9478</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-2</v>
+        <v>-1.9478</v>
       </c>
       <c r="I76" t="n">
-        <v>-2</v>
+        <v>-2.0312</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>117</v>
+        <v>417</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-2</v>
+        <v>-2.0312</v>
       </c>
       <c r="N76" t="n">
-        <v>117</v>
+        <v>417</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>THREAT</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-2.0037</v>
+        <v>-2</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.9833</v>
+        <v>-0.9815</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2308</v>
+        <v>-1.2407</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.0037</v>
+        <v>-2</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.4165</v>
+        <v>-2</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.4165</v>
+        <v>-2</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.4977</v>
+        <v>-2</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>555</v>
+        <v>117</v>
       </c>
       <c r="L77" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-2.0849</v>
+        <v>-2</v>
       </c>
       <c r="N77" t="n">
-        <v>628</v>
+        <v>117</v>
       </c>
     </row>
     <row r="78">
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.0554</v>
+        <v>-2.0023</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.0087</v>
+        <v>-0.9827</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2517</v>
+        <v>-1.2416</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.0554</v>
+        <v>-2.0023</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.0554</v>
+        <v>-2.0023</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.0554</v>
+        <v>-2.0023</v>
       </c>
       <c r="I78" t="n">
         <v>-2.1233</v>
@@ -4034,93 +4034,93 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.4948</v>
+        <v>-2.3194</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.2244</v>
+        <v>-1.1383</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.4292</v>
+        <v>-1.368</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.4948</v>
+        <v>-2.3194</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.0353</v>
+        <v>-4.3199</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.4595</v>
+        <v>2.0005</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.0353</v>
+        <v>-4.3199</v>
       </c>
       <c r="I79" t="n">
-        <v>-2.142</v>
+        <v>-4.7371</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.4595</v>
+        <v>2.0005</v>
       </c>
       <c r="K79" t="n">
-        <v>490</v>
+        <v>629</v>
       </c>
       <c r="L79" t="n">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.6015</v>
+        <v>-2.7366</v>
       </c>
       <c r="N79" t="n">
-        <v>658</v>
+        <v>717</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.5007</v>
+        <v>-2.4129</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.2273</v>
+        <v>-1.1842</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4316</v>
+        <v>-1.4052</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.5007</v>
+        <v>-2.4129</v>
       </c>
       <c r="F80" t="n">
-        <v>-4.5012</v>
+        <v>-1.9534</v>
       </c>
       <c r="G80" t="n">
-        <v>2.0005</v>
+        <v>-0.4595</v>
       </c>
       <c r="H80" t="n">
-        <v>-4.5012</v>
+        <v>-1.9534</v>
       </c>
       <c r="I80" t="n">
-        <v>-4.7371</v>
+        <v>-2.142</v>
       </c>
       <c r="J80" t="n">
-        <v>2.0005</v>
+        <v>-0.4595</v>
       </c>
       <c r="K80" t="n">
-        <v>629</v>
+        <v>490</v>
       </c>
       <c r="L80" t="n">
-        <v>88</v>
+        <v>168</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.7366</v>
+        <v>-2.6015</v>
       </c>
       <c r="N80" t="n">
-        <v>717</v>
+        <v>658</v>
       </c>
     </row>
     <row r="81">
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.4426</v>
+        <v>-3.3571</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.6895</v>
+        <v>-1.6476</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8121</v>
+        <v>-1.7814</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.4426</v>
+        <v>-3.3571</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.1229</v>
+        <v>-2.0374</v>
       </c>
       <c r="G81" t="n">
         <v>-1.3197</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.1229</v>
+        <v>-2.0374</v>
       </c>
       <c r="I81" t="n">
         <v>-2.2342</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-3.6276</v>
+        <v>-3.5604</v>
       </c>
       <c r="C82" t="n">
-        <v>-1.7803</v>
+        <v>-1.7473</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.8868</v>
+        <v>-1.8624</v>
       </c>
       <c r="E82" t="n">
-        <v>-3.6276</v>
+        <v>-3.5604</v>
       </c>
       <c r="F82" t="n">
-        <v>-3.6276</v>
+        <v>-3.5604</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-3.6276</v>
+        <v>-3.5604</v>
       </c>
       <c r="I82" t="n">
         <v>-3.7128</v>
@@ -4222,25 +4222,25 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-4.9198</v>
+        <v>-4.7405</v>
       </c>
       <c r="C83" t="n">
-        <v>-2.4145</v>
+        <v>-2.3265</v>
       </c>
       <c r="D83" t="n">
-        <v>-2.4089</v>
+        <v>-2.3325</v>
       </c>
       <c r="E83" t="n">
-        <v>-4.9198</v>
+        <v>-4.7405</v>
       </c>
       <c r="F83" t="n">
-        <v>-3.7809</v>
+        <v>-3.6016</v>
       </c>
       <c r="G83" t="n">
         <v>-1.1389</v>
       </c>
       <c r="H83" t="n">
-        <v>-3.7809</v>
+        <v>-3.6016</v>
       </c>
       <c r="I83" t="n">
         <v>-4.0162</v>
@@ -4264,93 +4264,93 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>oskarish</t>
+          <t>kRYSTAL</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-5.2802</v>
+        <v>-5.1591</v>
       </c>
       <c r="C84" t="n">
-        <v>-2.5913</v>
+        <v>-2.5319</v>
       </c>
       <c r="D84" t="n">
-        <v>-2.5544</v>
+        <v>-2.4993</v>
       </c>
       <c r="E84" t="n">
-        <v>-5.2802</v>
+        <v>-5.1591</v>
       </c>
       <c r="F84" t="n">
-        <v>-5.2802</v>
+        <v>-5.1591</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>-5.2802</v>
+        <v>-5.1591</v>
       </c>
       <c r="I84" t="n">
-        <v>-5.4294</v>
+        <v>-5.4708</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>473</v>
+        <v>499</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>-5.4294</v>
+        <v>-5.4708</v>
       </c>
       <c r="N84" t="n">
-        <v>473</v>
+        <v>499</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kRYSTAL</t>
+          <t>oskarish</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-5.2958</v>
+        <v>-5.1631</v>
       </c>
       <c r="C85" t="n">
-        <v>-2.599</v>
+        <v>-2.5339</v>
       </c>
       <c r="D85" t="n">
-        <v>-2.5607</v>
+        <v>-2.5009</v>
       </c>
       <c r="E85" t="n">
-        <v>-5.2958</v>
+        <v>-5.1631</v>
       </c>
       <c r="F85" t="n">
-        <v>-5.2958</v>
+        <v>-5.1631</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>-5.2958</v>
+        <v>-5.1631</v>
       </c>
       <c r="I85" t="n">
-        <v>-5.4708</v>
+        <v>-5.4294</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>499</v>
+        <v>473</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>-5.4708</v>
+        <v>-5.4294</v>
       </c>
       <c r="N85" t="n">
-        <v>499</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
